--- a/2_Risk_Management/MT-ISMS-IAR-001_v1.0_asset-register.xlsx
+++ b/2_Risk_Management/MT-ISMS-IAR-001_v1.0_asset-register.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="111">
   <si>
     <t>MunichTech GmbH</t>
   </si>
@@ -51,7 +51,7 @@
     <t>Effective Date</t>
   </si>
   <si>
-    <t>[Date]</t>
+    <t/>
   </si>
   <si>
     <t>Austin Bond, Junior GRC Consultant</t>
@@ -428,7 +428,7 @@
     <t>Approved By</t>
   </si>
   <si>
-    <t>[Senior GRC Partner Name], CISM, ISO LA</t>
+    <t>Dr. Andreas Kellermann, CISM, ISO LA</t>
   </si>
   <si>
     <t>CISO / Head of Engineering</t>
@@ -638,6 +638,9 @@
   </si>
   <si>
     <t>Marketing Director</t>
+  </si>
+  <si>
+    <t>5 November 2025</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1234,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>4</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="2:12">
